--- a/Firmware/Modules/EspLink/EspLink_State_Machine.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_State_Machine.xlsx
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -531,7 +531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -688,7 +688,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -854,7 +854,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/EspLink/EspLink_State_Machine.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_State_Machine.xlsx
@@ -858,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -976,17 +976,34 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>۲۰۴</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>فرمان ریست حکم باتری ضعیف (سناریوی ۸)؛ فقط حکم را پاک می‌کند و روی فلش نمی‌ماند</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>نکتهٔ ترتیب بوت</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>بازپخش NVM پیش از scheduler اجرا می‌شود، پس هیچ Init ماژولی نباید جدول پارامتر را دوباره بنویسد (ایراد IMB-1، اصلاح ۲۰۲۶-۱۰-۰۶)</t>
         </is>

--- a/Firmware/Modules/EspLink/EspLink_State_Machine.xlsx
+++ b/Firmware/Modules/EspLink/EspLink_State_Machine.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ پارسر" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ ماندگاری" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ پارسر" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ ماندگاری" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -858,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -927,7 +927,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>۲۰ تا ۱۳۱</t>
+          <t>۲۰ تا ۱۷۰</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -937,73 +937,90 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>به‌جز شناسهٔ ۷۶ (سکوت موقت) و ۷۲/۷۳ (بازنشسته)</t>
+          <t>به‌جز ۷۰ (مشتق از q34)، ۷۲/۷۳ (بازنشسته) و ۷۶ (سکوت موقت)؛ شامل ۱۴۳..۱۶۸ و حاشیه‌های مشترک ۱۶۹/۱۷۰</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>۷۰</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>آینهٔ فقط‌خواندنی سقف مشترک q34؛ جداگانه ذخیره نمی‌شود</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>۷۶</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>خیر</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>سکوت فقط برای همان نشست پنل است</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>۲۰۰ تا ۲۰۳</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>اسلات‌های حالت اجرا: شمارش‌های عدم‌توازن و پرچم باتری خراب</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>۲۰۴</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>خیر</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>فرمان ریست حکم باتری ضعیف (سناریوی ۸)؛ فقط حکم را پاک می‌کند و روی فلش نمی‌ماند</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>نکتهٔ ترتیب بوت</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>بازپخش NVM پیش از scheduler اجرا می‌شود، پس هیچ Init ماژولی نباید جدول پارامتر را دوباره بنویسد (ایراد IMB-1، اصلاح ۲۰۲۶-۱۰-۰۶)</t>
         </is>
